--- a/Demo/SCH-STH/demo_sppa_impact_2511_2_child.xlsx
+++ b/Demo/SCH-STH/demo_sppa_impact_2511_2_child.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldhealthorg-my.sharepoint.com/personal/yumbad_who_int/Documents/Desktop/to delete/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\SCH-STH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="13_ncr:1_{E9E98CF6-9054-4D01-97A7-97237706D41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{321A5F05-E58E-43E8-AF1F-BD64E05505DB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67D7A11-C1ED-4CF1-B7C3-1E1F93D24F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -339,9 +339,6 @@
     <t>demo_sppa_impact_2511_2_child</t>
   </si>
   <si>
-    <t>(2025 Oct) - 2. SCH/STH – Participant</t>
-  </si>
-  <si>
     <t>p_admin1</t>
   </si>
   <si>
@@ -1510,6 +1507,9 @@
   </si>
   <si>
     <t>p_Sample_collected</t>
+  </si>
+  <si>
+    <t>(Demo) - 2. SCH/STH – Participant</t>
   </si>
 </sst>
 </file>
@@ -2253,10 +2253,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>281</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>282</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>2</v>
@@ -2265,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>4</v>
@@ -2321,17 +2321,17 @@
         <v>9</v>
       </c>
       <c r="C2" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="62" t="s">
         <v>284</v>
-      </c>
-      <c r="D2" s="62" t="s">
-        <v>285</v>
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="23" t="s">
         <v>42</v>
       </c>
       <c r="G2" s="62" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H2" s="23"/>
       <c r="I2" s="23"/>
@@ -2356,10 +2356,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D3" s="62"/>
       <c r="E3" s="23"/>
@@ -2368,7 +2368,7 @@
       <c r="H3" s="23"/>
       <c r="I3" s="23"/>
       <c r="J3" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K3" s="23"/>
       <c r="L3" s="23"/>
@@ -2390,10 +2390,10 @@
         <v>11</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D4" s="59"/>
       <c r="E4" s="24"/>
@@ -2412,7 +2412,7 @@
         <v>68</v>
       </c>
       <c r="P4" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
@@ -2426,10 +2426,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="40" t="s">
         <v>291</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>292</v>
       </c>
       <c r="D5" s="41"/>
       <c r="E5" s="42"/>
@@ -2465,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D6" s="59"/>
       <c r="E6" s="24"/>
@@ -2501,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D7" s="59"/>
       <c r="E7" s="24"/>
@@ -2537,7 +2537,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="24"/>
@@ -2573,7 +2573,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D9" s="59"/>
       <c r="E9" s="23"/>
@@ -2597,16 +2597,16 @@
     </row>
     <row r="10" spans="1:22" s="11" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="C10" s="64" t="s">
         <v>302</v>
       </c>
-      <c r="C10" s="64" t="s">
+      <c r="D10" s="64" t="s">
         <v>303</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>304</v>
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="17"/>
@@ -2637,14 +2637,14 @@
         <v>93</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D11" s="64"/>
       <c r="E11" s="32"/>
       <c r="F11" s="17"/>
       <c r="G11" s="64"/>
       <c r="H11" s="32" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I11" s="32"/>
       <c r="J11" s="32" t="s">
@@ -2668,17 +2668,17 @@
         <v>92</v>
       </c>
       <c r="B12" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="64" t="s">
         <v>307</v>
-      </c>
-      <c r="C12" s="64" t="s">
-        <v>308</v>
       </c>
       <c r="D12" s="64"/>
       <c r="E12" s="32"/>
       <c r="F12" s="17"/>
       <c r="G12" s="64"/>
       <c r="H12" s="32" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I12" s="32"/>
       <c r="J12" s="32" t="s">
@@ -2766,10 +2766,10 @@
         <v>60</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="27"/>
@@ -2860,10 +2860,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="71" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" s="71" t="s">
         <v>298</v>
-      </c>
-      <c r="C18" s="71" t="s">
-        <v>299</v>
       </c>
       <c r="D18" s="71"/>
       <c r="E18" s="70"/>
@@ -2893,10 +2893,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19" s="64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
@@ -2924,17 +2924,17 @@
         <v>58</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="64"/>
       <c r="H20" s="34" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I20" s="32"/>
       <c r="J20" s="32" t="s">
@@ -2968,7 +2968,7 @@
       <c r="F21" s="35"/>
       <c r="G21" s="35"/>
       <c r="H21" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I21" s="35" t="s">
         <v>98</v>
@@ -3004,10 +3004,10 @@
       <c r="F22" s="35"/>
       <c r="G22" s="35"/>
       <c r="H22" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I22" s="35" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J22" s="35"/>
       <c r="K22" s="35"/>
@@ -3036,7 +3036,7 @@
       <c r="F23" s="34"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I23" s="34" t="s">
         <v>75</v>
@@ -3084,17 +3084,17 @@
         <v>18</v>
       </c>
       <c r="B25" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="44" t="s">
         <v>111</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>112</v>
       </c>
       <c r="D25" s="44"/>
       <c r="E25" s="44"/>
       <c r="F25" s="44"/>
       <c r="G25" s="44"/>
       <c r="H25" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I25" s="44"/>
       <c r="J25" s="44" t="s">
@@ -3118,7 +3118,7 @@
         <v>59</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C26" s="44"/>
       <c r="D26" s="44"/>
@@ -3126,10 +3126,10 @@
       <c r="F26" s="44"/>
       <c r="G26" s="44"/>
       <c r="H26" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I26" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J26" s="44"/>
       <c r="K26" s="44"/>
@@ -3171,20 +3171,20 @@
     </row>
     <row r="28" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="46" t="s">
+      <c r="C28" s="47" t="s">
         <v>115</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>116</v>
       </c>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
       <c r="F28" s="47"/>
       <c r="G28" s="47"/>
       <c r="H28" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I28" s="47"/>
       <c r="J28" s="47" t="s">
@@ -3205,20 +3205,20 @@
     </row>
     <row r="29" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="46" t="s">
+      <c r="C29" s="47" t="s">
         <v>118</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>119</v>
       </c>
       <c r="D29" s="47"/>
       <c r="E29" s="47"/>
       <c r="F29" s="47"/>
       <c r="G29" s="47"/>
       <c r="H29" s="46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I29" s="47"/>
       <c r="J29" s="47" t="s">
@@ -3242,17 +3242,17 @@
         <v>17</v>
       </c>
       <c r="B30" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="47" t="s">
         <v>120</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>121</v>
       </c>
       <c r="D30" s="47"/>
       <c r="E30" s="47"/>
       <c r="F30" s="47"/>
       <c r="G30" s="47"/>
       <c r="H30" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I30" s="47"/>
       <c r="J30" s="47" t="s">
@@ -3276,21 +3276,21 @@
         <v>17</v>
       </c>
       <c r="B31" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="48" t="s">
         <v>122</v>
-      </c>
-      <c r="C31" s="48" t="s">
-        <v>123</v>
       </c>
       <c r="D31" s="48"/>
       <c r="E31" s="48"/>
       <c r="F31" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="G31" s="48" t="s">
-        <v>125</v>
-      </c>
       <c r="H31" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I31" s="47"/>
       <c r="J31" s="48" t="s">
@@ -3341,7 +3341,7 @@
         <v>56</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="13"/>
@@ -3352,10 +3352,10 @@
         <v>87</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J33" s="14" t="s">
         <v>10</v>
@@ -3372,7 +3372,7 @@
       <c r="R33" s="17"/>
       <c r="S33" s="17"/>
       <c r="T33" s="33" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="U33" s="72" t="s">
         <v>76</v>
@@ -3411,20 +3411,20 @@
         <v>19</v>
       </c>
       <c r="C35" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="D35" s="63" t="s">
         <v>319</v>
-      </c>
-      <c r="D35" s="63" t="s">
-        <v>320</v>
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="G35" s="63" t="s">
         <v>321</v>
       </c>
-      <c r="G35" s="63" t="s">
-        <v>322</v>
-      </c>
       <c r="H35" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I35" s="24"/>
       <c r="J35" s="23" t="s">
@@ -3448,10 +3448,10 @@
         <v>18</v>
       </c>
       <c r="B36" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="C36" s="63" t="s">
         <v>326</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>327</v>
       </c>
       <c r="D36" s="59"/>
       <c r="E36" s="24"/>
@@ -3462,7 +3462,7 @@
         <v>54</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I36" s="24"/>
       <c r="J36" s="23" t="s">
@@ -3489,16 +3489,16 @@
         <v>21</v>
       </c>
       <c r="C37" s="63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D37" s="59"/>
       <c r="E37" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F37" s="24"/>
       <c r="G37" s="66"/>
       <c r="H37" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I37" s="24"/>
       <c r="J37" s="23" t="s">
@@ -3522,17 +3522,17 @@
         <v>11</v>
       </c>
       <c r="B38" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="C38" s="63" t="s">
         <v>324</v>
-      </c>
-      <c r="C38" s="63" t="s">
-        <v>325</v>
       </c>
       <c r="D38" s="59"/>
       <c r="E38" s="24"/>
       <c r="F38" s="24"/>
       <c r="G38" s="66"/>
       <c r="H38" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I38" s="24"/>
       <c r="J38" s="23" t="s">
@@ -3559,14 +3559,14 @@
         <v>43</v>
       </c>
       <c r="C39" s="63" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D39" s="59"/>
       <c r="E39" s="24"/>
       <c r="F39" s="24"/>
       <c r="G39" s="66"/>
       <c r="H39" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I39" s="24"/>
       <c r="J39" s="23" t="s">
@@ -3614,17 +3614,17 @@
         <v>14</v>
       </c>
       <c r="B41" s="71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C41" s="71" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D41" s="71"/>
       <c r="E41" s="70"/>
       <c r="F41" s="70"/>
       <c r="G41" s="71"/>
       <c r="H41" s="71" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I41" s="71"/>
       <c r="J41" s="71"/>
@@ -3643,20 +3643,20 @@
     </row>
     <row r="42" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C42" s="63" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D42" s="59"/>
       <c r="E42" s="24"/>
       <c r="F42" s="24"/>
       <c r="G42" s="66"/>
       <c r="H42" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I42" s="24"/>
       <c r="J42" s="23" t="s">
@@ -3680,19 +3680,19 @@
         <v>17</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C43" s="63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D43" s="59" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E43" s="24"/>
       <c r="F43" s="24"/>
       <c r="G43" s="66"/>
       <c r="H43" s="26" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I43" s="24"/>
       <c r="J43" s="23" t="s">
@@ -3713,20 +3713,20 @@
     </row>
     <row r="44" spans="1:22" s="6" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C44" s="63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D44" s="59"/>
       <c r="E44" s="24"/>
       <c r="F44" s="24"/>
       <c r="G44" s="66"/>
       <c r="H44" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="23" t="s">
@@ -3750,21 +3750,21 @@
         <v>17</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C45" s="63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" s="59"/>
       <c r="E45" s="24"/>
       <c r="F45" s="24"/>
       <c r="G45" s="66"/>
       <c r="H45" s="26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I45" s="24"/>
       <c r="J45" s="23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K45" s="24"/>
       <c r="L45" s="24"/>
@@ -3781,20 +3781,20 @@
     </row>
     <row r="46" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C46" s="63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D46" s="59"/>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="66"/>
       <c r="H46" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I46" s="24"/>
       <c r="J46" s="23" t="s">
@@ -3815,20 +3815,20 @@
     </row>
     <row r="47" spans="1:22" s="6" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C47" s="63" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D47" s="59"/>
       <c r="E47" s="24"/>
       <c r="F47" s="24"/>
       <c r="G47" s="66"/>
       <c r="H47" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I47" s="24"/>
       <c r="J47" s="23" t="s">
@@ -3849,20 +3849,20 @@
     </row>
     <row r="48" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>464</v>
+      </c>
+      <c r="C48" s="63" t="s">
         <v>204</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="C48" s="63" t="s">
-        <v>205</v>
       </c>
       <c r="D48" s="59"/>
       <c r="E48" s="24"/>
       <c r="F48" s="24"/>
       <c r="G48" s="66"/>
       <c r="H48" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I48" s="24"/>
       <c r="J48" s="23" t="s">
@@ -3883,20 +3883,20 @@
     </row>
     <row r="49" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>465</v>
+      </c>
+      <c r="C49" s="63" t="s">
         <v>206</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="C49" s="63" t="s">
-        <v>207</v>
       </c>
       <c r="D49" s="59"/>
       <c r="E49" s="24"/>
       <c r="F49" s="24"/>
       <c r="G49" s="66"/>
       <c r="H49" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I49" s="24"/>
       <c r="J49" s="23" t="s">
@@ -3944,17 +3944,17 @@
         <v>14</v>
       </c>
       <c r="B51" s="71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C51" s="71" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D51" s="71"/>
       <c r="E51" s="70"/>
       <c r="F51" s="70"/>
       <c r="G51" s="71"/>
       <c r="H51" s="71" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I51" s="71"/>
       <c r="J51" s="71"/>
@@ -3973,22 +3973,22 @@
     </row>
     <row r="52" spans="1:22" s="6" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C52" s="63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D52" s="59" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="24"/>
       <c r="G52" s="66"/>
       <c r="H52" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I52" s="24"/>
       <c r="J52" s="23" t="s">
@@ -4012,17 +4012,17 @@
         <v>17</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C53" s="63" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D53" s="59"/>
       <c r="E53" s="24"/>
       <c r="F53" s="24"/>
       <c r="G53" s="66"/>
       <c r="H53" s="26" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I53" s="24"/>
       <c r="J53" s="23" t="s">
@@ -4043,22 +4043,22 @@
     </row>
     <row r="54" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C54" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="D54" s="59" t="s">
         <v>232</v>
-      </c>
-      <c r="D54" s="59" t="s">
-        <v>233</v>
       </c>
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
       <c r="G54" s="66"/>
       <c r="H54" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I54" s="24"/>
       <c r="J54" s="23" t="s">
@@ -4079,22 +4079,22 @@
     </row>
     <row r="55" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C55" s="63" t="s">
+        <v>233</v>
+      </c>
+      <c r="D55" s="59" t="s">
         <v>234</v>
-      </c>
-      <c r="D55" s="59" t="s">
-        <v>235</v>
       </c>
       <c r="E55" s="24"/>
       <c r="F55" s="24"/>
       <c r="G55" s="66"/>
       <c r="H55" s="26" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I55" s="24"/>
       <c r="J55" s="23" t="s">
@@ -4142,17 +4142,17 @@
         <v>14</v>
       </c>
       <c r="B57" s="71" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C57" s="71" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D57" s="71"/>
       <c r="E57" s="70"/>
       <c r="F57" s="70"/>
       <c r="G57" s="71"/>
       <c r="H57" s="71" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I57" s="71"/>
       <c r="J57" s="71"/>
@@ -4171,22 +4171,22 @@
     </row>
     <row r="58" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="37" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C58" s="74" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D58" s="74" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E58" s="31"/>
       <c r="F58" s="31"/>
       <c r="G58" s="74"/>
       <c r="H58" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I58" s="31"/>
       <c r="J58" s="30" t="s">
@@ -4210,17 +4210,17 @@
         <v>17</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C59" s="74" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D59" s="74"/>
       <c r="E59" s="31"/>
       <c r="F59" s="31"/>
       <c r="G59" s="74"/>
       <c r="H59" s="29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I59" s="31"/>
       <c r="J59" s="30" t="s">
@@ -4244,19 +4244,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C60" s="74" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D60" s="74"/>
       <c r="E60" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F60" s="31"/>
       <c r="G60" s="74"/>
       <c r="H60" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I60" s="31"/>
       <c r="J60" s="30" t="s">
@@ -4277,20 +4277,20 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="C61" s="74" t="s">
         <v>258</v>
-      </c>
-      <c r="B61" s="30" t="s">
-        <v>477</v>
-      </c>
-      <c r="C61" s="74" t="s">
-        <v>259</v>
       </c>
       <c r="D61" s="74"/>
       <c r="E61" s="31"/>
       <c r="F61" s="31"/>
       <c r="G61" s="74"/>
       <c r="H61" s="26" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I61" s="31"/>
       <c r="J61" s="30" t="s">
@@ -4311,20 +4311,20 @@
     </row>
     <row r="62" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A62" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="C62" s="76" t="s">
         <v>278</v>
-      </c>
-      <c r="B62" s="30" t="s">
-        <v>479</v>
-      </c>
-      <c r="C62" s="76" t="s">
-        <v>279</v>
       </c>
       <c r="D62" s="74"/>
       <c r="E62" s="31"/>
       <c r="F62" s="31"/>
       <c r="G62" s="74"/>
       <c r="H62" s="29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I62" s="31"/>
       <c r="J62" s="30" t="s">
@@ -4348,17 +4348,17 @@
         <v>17</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C63" s="74" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D63" s="74"/>
       <c r="E63" s="31"/>
       <c r="F63" s="31"/>
       <c r="G63" s="74"/>
       <c r="H63" s="29" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I63" s="31"/>
       <c r="J63" s="30" t="s">
@@ -4382,19 +4382,19 @@
         <v>58</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C64" s="63" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D64" s="59"/>
       <c r="E64" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F64" s="24"/>
       <c r="G64" s="66"/>
       <c r="H64" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I64" s="24"/>
       <c r="J64" s="30" t="s">
@@ -4418,19 +4418,19 @@
         <v>58</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C65" s="63" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D65" s="59"/>
       <c r="E65" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F65" s="24"/>
       <c r="G65" s="66"/>
       <c r="H65" s="26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I65" s="24"/>
       <c r="J65" s="30" t="s">
@@ -4451,20 +4451,20 @@
     </row>
     <row r="66" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>484</v>
+      </c>
+      <c r="C66" s="63" t="s">
         <v>270</v>
-      </c>
-      <c r="B66" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="C66" s="63" t="s">
-        <v>271</v>
       </c>
       <c r="D66" s="59"/>
       <c r="E66" s="24"/>
       <c r="F66" s="24"/>
       <c r="G66" s="66"/>
       <c r="H66" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I66" s="24"/>
       <c r="J66" s="30" t="s">
@@ -4485,20 +4485,20 @@
     </row>
     <row r="67" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>485</v>
+      </c>
+      <c r="C67" s="63" t="s">
         <v>272</v>
-      </c>
-      <c r="B67" s="26" t="s">
-        <v>486</v>
-      </c>
-      <c r="C67" s="63" t="s">
-        <v>273</v>
       </c>
       <c r="D67" s="59"/>
       <c r="E67" s="24"/>
       <c r="F67" s="24"/>
       <c r="G67" s="66"/>
       <c r="H67" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I67" s="24"/>
       <c r="J67" s="30" t="s">
@@ -4519,20 +4519,20 @@
     </row>
     <row r="68" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>486</v>
+      </c>
+      <c r="C68" s="63" t="s">
         <v>274</v>
-      </c>
-      <c r="B68" s="26" t="s">
-        <v>487</v>
-      </c>
-      <c r="C68" s="63" t="s">
-        <v>275</v>
       </c>
       <c r="D68" s="59"/>
       <c r="E68" s="24"/>
       <c r="F68" s="24"/>
       <c r="G68" s="66"/>
       <c r="H68" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I68" s="24"/>
       <c r="J68" s="30" t="s">
@@ -4580,19 +4580,19 @@
         <v>58</v>
       </c>
       <c r="B70" s="26" t="s">
+        <v>436</v>
+      </c>
+      <c r="C70" s="63" t="s">
         <v>437</v>
-      </c>
-      <c r="C70" s="63" t="s">
-        <v>438</v>
       </c>
       <c r="D70" s="59"/>
       <c r="E70" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F70" s="24"/>
       <c r="G70" s="66"/>
       <c r="H70" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I70" s="24"/>
       <c r="J70" s="26" t="s">
@@ -4619,14 +4619,14 @@
         <v>49</v>
       </c>
       <c r="C71" s="63" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D71" s="59"/>
       <c r="E71" s="24"/>
       <c r="F71" s="24"/>
       <c r="G71" s="66"/>
       <c r="H71" s="26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I71" s="24"/>
       <c r="J71" s="26" t="s">
@@ -4650,19 +4650,19 @@
         <v>58</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C72" s="63" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D72" s="59"/>
       <c r="E72" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F72" s="24"/>
       <c r="G72" s="66"/>
       <c r="H72" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I72" s="24"/>
       <c r="J72" s="26" t="s">
@@ -4686,19 +4686,19 @@
         <v>58</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C73" s="63" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D73" s="59"/>
       <c r="E73" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F73" s="24"/>
       <c r="G73" s="66"/>
       <c r="H73" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I73" s="24"/>
       <c r="J73" s="26" t="s">
@@ -4722,19 +4722,19 @@
         <v>58</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C74" s="63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D74" s="59"/>
       <c r="E74" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F74" s="24"/>
       <c r="G74" s="66"/>
       <c r="H74" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I74" s="24"/>
       <c r="J74" s="26" t="s">
@@ -4758,19 +4758,19 @@
         <v>58</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C75" s="63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D75" s="59"/>
       <c r="E75" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F75" s="24"/>
       <c r="G75" s="66"/>
       <c r="H75" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I75" s="24"/>
       <c r="J75" s="26" t="s">
@@ -4794,17 +4794,17 @@
         <v>18</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C76" s="63" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D76" s="59"/>
       <c r="E76" s="24"/>
       <c r="F76" s="24"/>
       <c r="G76" s="66"/>
       <c r="H76" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I76" s="24"/>
       <c r="J76" s="26"/>
@@ -4826,19 +4826,19 @@
         <v>58</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C77" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D77" s="74"/>
       <c r="E77" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F77" s="31"/>
       <c r="G77" s="74"/>
       <c r="H77" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I77" s="31"/>
       <c r="J77" s="30" t="s">
@@ -4862,19 +4862,19 @@
         <v>58</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C78" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D78" s="59"/>
       <c r="E78" s="73" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F78" s="24"/>
       <c r="G78" s="66"/>
       <c r="H78" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I78" s="24"/>
       <c r="J78" s="26"/>
@@ -4893,20 +4893,20 @@
     </row>
     <row r="79" spans="1:22" s="6" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="C79" s="63" t="s">
         <v>276</v>
-      </c>
-      <c r="B79" s="26" t="s">
-        <v>493</v>
-      </c>
-      <c r="C79" s="63" t="s">
-        <v>277</v>
       </c>
       <c r="D79" s="59"/>
       <c r="E79" s="24"/>
       <c r="F79" s="24"/>
       <c r="G79" s="66"/>
       <c r="H79" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I79" s="24"/>
       <c r="J79" s="30" t="s">
@@ -4994,7 +4994,7 @@
       <c r="F82" s="30"/>
       <c r="G82" s="68"/>
       <c r="H82" s="25" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I82" s="30"/>
       <c r="J82" s="30"/>
@@ -5026,7 +5026,7 @@
       <c r="F83" s="30"/>
       <c r="G83" s="68"/>
       <c r="H83" s="26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I83" s="30"/>
       <c r="J83" s="30"/>
@@ -5107,7 +5107,7 @@
       <c r="G86" s="34"/>
       <c r="H86" s="26"/>
       <c r="I86" s="34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J86" s="34"/>
       <c r="K86" s="34"/>
@@ -5205,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D1" s="51" t="s">
         <v>41</v>
@@ -5225,10 +5225,10 @@
         <v>31</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" s="49"/>
     </row>
@@ -5237,46 +5237,46 @@
         <v>31</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D3" s="49"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D4" s="49"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D5" s="49"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D6" s="49"/>
     </row>
@@ -5288,37 +5288,37 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="56" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="C8" s="57" t="s">
         <v>129</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>130</v>
       </c>
       <c r="D8" s="50"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="56" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D9" s="50"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="57" t="s">
         <v>132</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>133</v>
       </c>
       <c r="D10" s="50"/>
     </row>
@@ -5336,7 +5336,7 @@
         <v>89</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" s="50"/>
     </row>
@@ -5348,7 +5348,7 @@
         <v>90</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D13" s="50"/>
     </row>
@@ -5363,10 +5363,10 @@
         <v>101</v>
       </c>
       <c r="B15" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="55" t="s">
         <v>136</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>137</v>
       </c>
       <c r="D15" s="50"/>
     </row>
@@ -5381,10 +5381,10 @@
         <v>45</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D17" s="49"/>
     </row>
@@ -5393,10 +5393,10 @@
         <v>45</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D18" s="49"/>
     </row>
@@ -5405,10 +5405,10 @@
         <v>45</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D19" s="49"/>
     </row>
@@ -5450,145 +5450,145 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B24" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="54" t="s">
         <v>147</v>
-      </c>
-      <c r="C24" s="54" t="s">
-        <v>148</v>
       </c>
       <c r="D24" s="49"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="54" t="s">
         <v>149</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>150</v>
       </c>
       <c r="D25" s="49"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B26" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="54" t="s">
         <v>151</v>
-      </c>
-      <c r="C26" s="54" t="s">
-        <v>152</v>
       </c>
       <c r="D26" s="49"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" s="54" t="s">
         <v>153</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>154</v>
       </c>
       <c r="D27" s="49"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B28" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="54" t="s">
         <v>155</v>
-      </c>
-      <c r="C28" s="54" t="s">
-        <v>156</v>
       </c>
       <c r="D28" s="49"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B29" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="54" t="s">
         <v>157</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>158</v>
       </c>
       <c r="D29" s="49"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="54" t="s">
         <v>159</v>
-      </c>
-      <c r="C30" s="54" t="s">
-        <v>160</v>
       </c>
       <c r="D30" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B31" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="54" t="s">
         <v>161</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>162</v>
       </c>
       <c r="D31" s="49"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B32" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="54" t="s">
         <v>163</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>164</v>
       </c>
       <c r="D32" s="49"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B33" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="54" t="s">
         <v>165</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>166</v>
       </c>
       <c r="D33" s="49"/>
     </row>
     <row r="34" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A34" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="54" t="s">
         <v>167</v>
-      </c>
-      <c r="C34" s="54" t="s">
-        <v>168</v>
       </c>
       <c r="D34" s="49"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D35" s="49"/>
     </row>
@@ -5600,133 +5600,133 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" s="54" t="s">
         <v>171</v>
-      </c>
-      <c r="C37" s="54" t="s">
-        <v>172</v>
       </c>
       <c r="D37" s="49"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B38" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="54" t="s">
         <v>173</v>
-      </c>
-      <c r="C38" s="54" t="s">
-        <v>174</v>
       </c>
       <c r="D38" s="49"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B39" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="54" t="s">
         <v>175</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>176</v>
       </c>
       <c r="D39" s="49"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B40" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="54" t="s">
         <v>177</v>
-      </c>
-      <c r="C40" s="54" t="s">
-        <v>178</v>
       </c>
       <c r="D40" s="49"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D41" s="49"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B42" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="54" t="s">
         <v>157</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>158</v>
       </c>
       <c r="D42" s="49"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B43" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" s="54" t="s">
         <v>159</v>
-      </c>
-      <c r="C43" s="54" t="s">
-        <v>160</v>
       </c>
       <c r="D43" s="49"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B44" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" s="54" t="s">
         <v>180</v>
-      </c>
-      <c r="C44" s="54" t="s">
-        <v>181</v>
       </c>
       <c r="D44" s="49"/>
     </row>
     <row r="45" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A45" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B45" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C45" s="54" t="s">
         <v>182</v>
-      </c>
-      <c r="C45" s="54" t="s">
-        <v>183</v>
       </c>
       <c r="D45" s="49"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C46" s="54" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D46" s="49"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D47" s="49"/>
     </row>
@@ -5738,49 +5738,49 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B49" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="C49" s="55" t="s">
         <v>334</v>
-      </c>
-      <c r="C49" s="55" t="s">
-        <v>335</v>
       </c>
       <c r="D49" s="50"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B50" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="C50" s="55" t="s">
         <v>336</v>
-      </c>
-      <c r="C50" s="55" t="s">
-        <v>337</v>
       </c>
       <c r="D50" s="50"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B51" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="C51" s="55" t="s">
         <v>338</v>
-      </c>
-      <c r="C51" s="55" t="s">
-        <v>339</v>
       </c>
       <c r="D51" s="50"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B52" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="C52" s="55" t="s">
         <v>340</v>
-      </c>
-      <c r="C52" s="55" t="s">
-        <v>341</v>
       </c>
       <c r="D52" s="50"/>
     </row>
@@ -5792,61 +5792,61 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B54" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B54" s="30" t="s">
+      <c r="C54" s="55" t="s">
         <v>194</v>
-      </c>
-      <c r="C54" s="55" t="s">
-        <v>195</v>
       </c>
       <c r="D54" s="49"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B55" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="55" t="s">
         <v>196</v>
-      </c>
-      <c r="C55" s="55" t="s">
-        <v>197</v>
       </c>
       <c r="D55" s="49"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" s="55" t="s">
         <v>198</v>
-      </c>
-      <c r="C56" s="55" t="s">
-        <v>199</v>
       </c>
       <c r="D56" s="49"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B57" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="C57" s="55" t="s">
         <v>200</v>
-      </c>
-      <c r="C57" s="55" t="s">
-        <v>201</v>
       </c>
       <c r="D57" s="49"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B58" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58" s="55" t="s">
         <v>202</v>
-      </c>
-      <c r="C58" s="55" t="s">
-        <v>203</v>
       </c>
       <c r="D58" s="49"/>
     </row>
@@ -5858,109 +5858,109 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B60" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="B60" s="30" t="s">
+      <c r="C60" s="55" t="s">
         <v>209</v>
-      </c>
-      <c r="C60" s="55" t="s">
-        <v>210</v>
       </c>
       <c r="D60" s="50"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B61" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" s="55" t="s">
         <v>211</v>
-      </c>
-      <c r="C61" s="55" t="s">
-        <v>212</v>
       </c>
       <c r="D61" s="50"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="C62" s="55" t="s">
         <v>213</v>
-      </c>
-      <c r="C62" s="55" t="s">
-        <v>214</v>
       </c>
       <c r="D62" s="50"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B63" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="C63" s="55" t="s">
         <v>215</v>
-      </c>
-      <c r="C63" s="55" t="s">
-        <v>216</v>
       </c>
       <c r="D63" s="50"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B64" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="55" t="s">
         <v>217</v>
-      </c>
-      <c r="C64" s="55" t="s">
-        <v>218</v>
       </c>
       <c r="D64" s="50"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B65" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="55" t="s">
         <v>219</v>
-      </c>
-      <c r="C65" s="55" t="s">
-        <v>220</v>
       </c>
       <c r="D65" s="50"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B66" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="C66" s="55" t="s">
         <v>221</v>
-      </c>
-      <c r="C66" s="55" t="s">
-        <v>222</v>
       </c>
       <c r="D66" s="50"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B67" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C67" s="55" t="s">
         <v>223</v>
-      </c>
-      <c r="C67" s="55" t="s">
-        <v>224</v>
       </c>
       <c r="D67" s="50"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B68" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" s="55" t="s">
         <v>225</v>
-      </c>
-      <c r="C68" s="55" t="s">
-        <v>226</v>
       </c>
       <c r="D68" s="50"/>
     </row>
@@ -5972,37 +5972,37 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="B70" s="30" t="s">
-        <v>228</v>
-      </c>
       <c r="C70" s="55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D70" s="50"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D71" s="50"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C72" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D72" s="50"/>
     </row>
@@ -6014,121 +6014,121 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="60" t="s">
+        <v>421</v>
+      </c>
+      <c r="B74" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="B74" s="23" t="s">
-        <v>423</v>
-      </c>
       <c r="C74" s="54" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D74" s="49"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C75" s="54" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D75" s="49"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C76" s="54" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D76" s="49"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C77" s="54" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D77" s="49"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C78" s="54" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D78" s="49"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C79" s="54" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D79" s="49"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="60" t="s">
+        <v>421</v>
+      </c>
+      <c r="B80" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="B80" s="23" t="s">
-        <v>423</v>
-      </c>
       <c r="C80" s="54" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D80" s="49"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C81" s="58" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D81" s="49"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B82" s="26" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C82" s="58" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D82" s="49"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="60" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C83" s="58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D83" s="49"/>
     </row>
@@ -6140,133 +6140,133 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B85" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C85" s="55" t="s">
         <v>237</v>
-      </c>
-      <c r="C85" s="55" t="s">
-        <v>238</v>
       </c>
       <c r="D85" s="50"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B86" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C86" s="55" t="s">
         <v>239</v>
-      </c>
-      <c r="C86" s="55" t="s">
-        <v>240</v>
       </c>
       <c r="D86" s="50"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B87" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="C87" s="55" t="s">
         <v>241</v>
-      </c>
-      <c r="C87" s="55" t="s">
-        <v>242</v>
       </c>
       <c r="D87" s="50"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B88" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="C88" s="55" t="s">
         <v>243</v>
-      </c>
-      <c r="C88" s="55" t="s">
-        <v>244</v>
       </c>
       <c r="D88" s="50"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B89" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="C89" s="55" t="s">
         <v>245</v>
-      </c>
-      <c r="C89" s="55" t="s">
-        <v>246</v>
       </c>
       <c r="D89" s="50"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B90" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C90" s="55" t="s">
         <v>247</v>
-      </c>
-      <c r="C90" s="55" t="s">
-        <v>248</v>
       </c>
       <c r="D90" s="50"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B91" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="C91" s="55" t="s">
         <v>249</v>
-      </c>
-      <c r="C91" s="55" t="s">
-        <v>250</v>
       </c>
       <c r="D91" s="50"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B92" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="C92" s="55" t="s">
         <v>251</v>
-      </c>
-      <c r="C92" s="55" t="s">
-        <v>252</v>
       </c>
       <c r="D92" s="50"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B93" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C93" s="55" t="s">
         <v>253</v>
-      </c>
-      <c r="C93" s="55" t="s">
-        <v>254</v>
       </c>
       <c r="D93" s="50"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B94" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="C94" s="55" t="s">
         <v>255</v>
-      </c>
-      <c r="C94" s="55" t="s">
-        <v>256</v>
       </c>
       <c r="D94" s="50"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B95" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C95" s="55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D95" s="50"/>
     </row>
@@ -6278,37 +6278,37 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="B97" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="B97" s="23" t="s">
+      <c r="C97" s="54" t="s">
         <v>261</v>
-      </c>
-      <c r="C97" s="54" t="s">
-        <v>262</v>
       </c>
       <c r="D97" s="49"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B98" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="C98" s="54" t="s">
         <v>263</v>
-      </c>
-      <c r="C98" s="54" t="s">
-        <v>264</v>
       </c>
       <c r="D98" s="49"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B99" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" s="54" t="s">
         <v>265</v>
-      </c>
-      <c r="C99" s="54" t="s">
-        <v>266</v>
       </c>
       <c r="D99" s="49"/>
     </row>
@@ -6320,97 +6320,97 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B101" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="B101" s="30" t="s">
+      <c r="C101" s="55" t="s">
         <v>355</v>
-      </c>
-      <c r="C101" s="55" t="s">
-        <v>356</v>
       </c>
       <c r="D101" s="50"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B102" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="C102" s="55" t="s">
         <v>357</v>
-      </c>
-      <c r="C102" s="55" t="s">
-        <v>358</v>
       </c>
       <c r="D102" s="50"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B103" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C103" s="55" t="s">
         <v>359</v>
-      </c>
-      <c r="C103" s="55" t="s">
-        <v>360</v>
       </c>
       <c r="D103" s="50"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B104" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="C104" s="55" t="s">
         <v>361</v>
-      </c>
-      <c r="C104" s="55" t="s">
-        <v>362</v>
       </c>
       <c r="D104" s="50"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B105" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C105" s="55" t="s">
         <v>363</v>
-      </c>
-      <c r="C105" s="55" t="s">
-        <v>364</v>
       </c>
       <c r="D105" s="50"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B106" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="C106" s="55" t="s">
         <v>365</v>
-      </c>
-      <c r="C106" s="55" t="s">
-        <v>366</v>
       </c>
       <c r="D106" s="50"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B107" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C107" s="55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D107" s="50"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B108" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C108" s="55" t="s">
         <v>225</v>
-      </c>
-      <c r="C108" s="55" t="s">
-        <v>226</v>
       </c>
       <c r="D108" s="50"/>
     </row>
@@ -6422,97 +6422,97 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B110" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="B110" s="30" t="s">
+      <c r="C110" s="55" t="s">
         <v>355</v>
-      </c>
-      <c r="C110" s="55" t="s">
-        <v>356</v>
       </c>
       <c r="D110" s="50"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B111" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="C111" s="55" t="s">
         <v>357</v>
-      </c>
-      <c r="C111" s="55" t="s">
-        <v>358</v>
       </c>
       <c r="D111" s="50"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B112" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C112" s="55" t="s">
         <v>359</v>
-      </c>
-      <c r="C112" s="55" t="s">
-        <v>360</v>
       </c>
       <c r="D112" s="50"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B113" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="C113" s="55" t="s">
         <v>361</v>
-      </c>
-      <c r="C113" s="55" t="s">
-        <v>362</v>
       </c>
       <c r="D113" s="50"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B114" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C114" s="55" t="s">
         <v>363</v>
-      </c>
-      <c r="C114" s="55" t="s">
-        <v>364</v>
       </c>
       <c r="D114" s="50"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B115" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="C115" s="55" t="s">
         <v>365</v>
-      </c>
-      <c r="C115" s="55" t="s">
-        <v>366</v>
       </c>
       <c r="D115" s="50"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C116" s="55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D116" s="50"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B117" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C117" s="55" t="s">
         <v>225</v>
-      </c>
-      <c r="C117" s="55" t="s">
-        <v>226</v>
       </c>
       <c r="D117" s="50"/>
     </row>
@@ -6524,169 +6524,169 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B119" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="B119" s="30" t="s">
+      <c r="C119" s="55" t="s">
         <v>369</v>
-      </c>
-      <c r="C119" s="55" t="s">
-        <v>370</v>
       </c>
       <c r="D119" s="50"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B120" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="C120" s="55" t="s">
         <v>371</v>
-      </c>
-      <c r="C120" s="55" t="s">
-        <v>372</v>
       </c>
       <c r="D120" s="50"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B121" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="C121" s="55" t="s">
         <v>373</v>
-      </c>
-      <c r="C121" s="55" t="s">
-        <v>374</v>
       </c>
       <c r="D121" s="50"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B122" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="C122" s="55" t="s">
         <v>375</v>
-      </c>
-      <c r="C122" s="55" t="s">
-        <v>376</v>
       </c>
       <c r="D122" s="50"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B123" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="55" t="s">
         <v>377</v>
-      </c>
-      <c r="C123" s="55" t="s">
-        <v>378</v>
       </c>
       <c r="D123" s="50"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B124" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="C124" s="55" t="s">
         <v>379</v>
-      </c>
-      <c r="C124" s="55" t="s">
-        <v>380</v>
       </c>
       <c r="D124" s="50"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B125" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="C125" s="55" t="s">
         <v>381</v>
-      </c>
-      <c r="C125" s="55" t="s">
-        <v>382</v>
       </c>
       <c r="D125" s="50"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B126" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="C126" s="55" t="s">
         <v>383</v>
-      </c>
-      <c r="C126" s="55" t="s">
-        <v>384</v>
       </c>
       <c r="D126" s="50"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B127" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C127" s="55" t="s">
         <v>385</v>
-      </c>
-      <c r="C127" s="55" t="s">
-        <v>386</v>
       </c>
       <c r="D127" s="50"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B128" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="C128" s="55" t="s">
         <v>387</v>
-      </c>
-      <c r="C128" s="55" t="s">
-        <v>388</v>
       </c>
       <c r="D128" s="50"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B129" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="C129" s="55" t="s">
         <v>389</v>
-      </c>
-      <c r="C129" s="55" t="s">
-        <v>390</v>
       </c>
       <c r="D129" s="50"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B130" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="C130" s="55" t="s">
         <v>391</v>
-      </c>
-      <c r="C130" s="55" t="s">
-        <v>392</v>
       </c>
       <c r="D130" s="50"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B131" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="C131" s="55" t="s">
         <v>393</v>
-      </c>
-      <c r="C131" s="55" t="s">
-        <v>394</v>
       </c>
       <c r="D131" s="50"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B132" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="C132" s="55" t="s">
         <v>395</v>
-      </c>
-      <c r="C132" s="55" t="s">
-        <v>396</v>
       </c>
       <c r="D132" s="50"/>
     </row>
@@ -6698,73 +6698,73 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="B134" s="30" t="s">
         <v>397</v>
       </c>
-      <c r="B134" s="30" t="s">
+      <c r="C134" s="55" t="s">
         <v>398</v>
-      </c>
-      <c r="C134" s="55" t="s">
-        <v>399</v>
       </c>
       <c r="D134" s="50"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B135" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="C135" s="55" t="s">
         <v>400</v>
-      </c>
-      <c r="C135" s="55" t="s">
-        <v>401</v>
       </c>
       <c r="D135" s="50"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B136" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="C136" s="55" t="s">
         <v>402</v>
-      </c>
-      <c r="C136" s="55" t="s">
-        <v>403</v>
       </c>
       <c r="D136" s="50"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B137" s="30" t="s">
+        <v>403</v>
+      </c>
+      <c r="C137" s="55" t="s">
         <v>404</v>
-      </c>
-      <c r="C137" s="55" t="s">
-        <v>405</v>
       </c>
       <c r="D137" s="50"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B138" s="30" t="s">
+        <v>405</v>
+      </c>
+      <c r="C138" s="55" t="s">
         <v>406</v>
-      </c>
-      <c r="C138" s="55" t="s">
-        <v>407</v>
       </c>
       <c r="D138" s="50"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B139" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C139" s="55" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D139" s="50"/>
     </row>
@@ -6776,49 +6776,49 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="30" t="s">
+        <v>408</v>
+      </c>
+      <c r="B141" s="30" t="s">
         <v>409</v>
       </c>
-      <c r="B141" s="30" t="s">
+      <c r="C141" s="55" t="s">
         <v>410</v>
-      </c>
-      <c r="C141" s="55" t="s">
-        <v>411</v>
       </c>
       <c r="D141" s="50"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="30" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B142" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="C142" s="55" t="s">
         <v>412</v>
-      </c>
-      <c r="C142" s="55" t="s">
-        <v>413</v>
       </c>
       <c r="D142" s="50"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="30" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B143" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="C143" s="55" t="s">
         <v>414</v>
-      </c>
-      <c r="C143" s="55" t="s">
-        <v>415</v>
       </c>
       <c r="D143" s="50"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="30" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B144" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="C144" s="55" t="s">
         <v>416</v>
-      </c>
-      <c r="C144" s="55" t="s">
-        <v>417</v>
       </c>
       <c r="D144" s="50"/>
     </row>
@@ -6830,25 +6830,25 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="30" t="s">
+        <v>417</v>
+      </c>
+      <c r="B146" s="30" t="s">
         <v>418</v>
       </c>
-      <c r="B146" s="30" t="s">
-        <v>419</v>
-      </c>
       <c r="C146" s="55" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D146" s="50"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="30" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B147" s="30" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C147" s="55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D147" s="50"/>
     </row>
@@ -6863,10 +6863,10 @@
         <v>46</v>
       </c>
       <c r="B149" s="26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C149" s="58" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D149" s="49"/>
     </row>
@@ -6875,10 +6875,10 @@
         <v>46</v>
       </c>
       <c r="B150" s="26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C150" s="54" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D150" s="49"/>
     </row>
@@ -6887,10 +6887,10 @@
         <v>46</v>
       </c>
       <c r="B151" s="26" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C151" s="54" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D151" s="49"/>
     </row>
@@ -6899,10 +6899,10 @@
         <v>46</v>
       </c>
       <c r="B152" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C152" s="58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D152" s="49"/>
     </row>
@@ -6954,18 +6954,18 @@
         <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>493</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>10</v>

--- a/Demo/SCH-STH/demo_sppa_impact_2511_2_child.xlsx
+++ b/Demo/SCH-STH/demo_sppa_impact_2511_2_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\SCH-STH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67D7A11-C1ED-4CF1-B7C3-1E1F93D24F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100A0CB9-EA90-4BE2-82BE-F49557DF0565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -3374,10 +3374,10 @@
       <c r="T33" s="33" t="s">
         <v>453</v>
       </c>
-      <c r="U33" s="72" t="s">
+      <c r="U33" s="33"/>
+      <c r="V33" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="V33" s="17"/>
     </row>
     <row r="34" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>

--- a/Demo/SCH-STH/demo_sppa_impact_2511_2_child.xlsx
+++ b/Demo/SCH-STH/demo_sppa_impact_2511_2_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\SCH-STH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100A0CB9-EA90-4BE2-82BE-F49557DF0565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65B57EB-CD0C-424D-A6AC-EB23CFB79653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -3371,10 +3371,10 @@
       <c r="Q33" s="17"/>
       <c r="R33" s="17"/>
       <c r="S33" s="17"/>
-      <c r="T33" s="33" t="s">
+      <c r="T33" s="33"/>
+      <c r="U33" s="33" t="s">
         <v>453</v>
       </c>
-      <c r="U33" s="33"/>
       <c r="V33" s="72" t="s">
         <v>76</v>
       </c>
